--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -52794,13 +52794,13 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O296" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R296" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -52958,10 +52958,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O297" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U297" t="inlineStr">
         <is>
@@ -53561,12 +53561,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -53600,81 +53600,100 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="O300" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="R300" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR300" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS300" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -53701,17 +53720,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -53736,7 +53755,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -53745,81 +53764,175 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>272</v>
+        <v>22</v>
       </c>
       <c r="O301" t="n">
-        <v>272</v>
-      </c>
-      <c r="R301" t="n">
-        <v>0.2221718868578884</v>
-      </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ301" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM301" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN301" t="b">
+        <v>1</v>
       </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ301" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR301" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS301" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -53881,7 +53994,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -53890,13 +54003,13 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="O302" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R302" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
@@ -54026,7 +54139,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -54035,13 +54148,13 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="O303" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="R303" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -54171,7 +54284,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -54180,13 +54293,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="O304" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="R304" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -54316,7 +54429,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -54325,13 +54438,13 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="O305" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="R305" t="n">
-        <v>0.1511095553996668</v>
+        <v>0.2033852934838758</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -54461,7 +54574,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -54470,13 +54583,13 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O306" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="R306" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -54606,7 +54719,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -54615,13 +54728,13 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="O307" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="R307" t="n">
-        <v>0.1960340178157839</v>
+        <v>0.1511095553996668</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -54751,7 +54864,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -54760,13 +54873,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="O308" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="R308" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -54866,12 +54979,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -54896,22 +55009,22 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N309" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="O309" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="R309" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.1960340178157839</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -54944,42 +55057,42 @@
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55011,12 +55124,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -55041,109 +55154,90 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N310" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="O310" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="R310" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA310" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO310" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP310" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ310" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR310" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS310" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr"/>
       <c r="AT310" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55170,17 +55264,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -55214,175 +55308,81 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O311" t="n">
-        <v>4</v>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y311" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA311" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC311" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0.04407374183423748</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP311" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR311" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS311" t="inlineStr"/>
+      <c r="AT311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU311" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV311" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE311" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ311" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK311" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM311" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN311" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO311" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP311" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ311" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR311" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS311" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AT311" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU311" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV311" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -55414,12 +55414,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -55453,13 +55453,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R312" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -55488,7 +55488,7 @@
       </c>
       <c r="AQ312" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR312" t="inlineStr">
@@ -55498,7 +55498,7 @@
       </c>
       <c r="AS312" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT312" t="n">
@@ -55506,47 +55506,47 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -55578,12 +55578,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -55617,29 +55617,29 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O313" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y313" t="inlineStr">
@@ -55664,7 +55664,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD313" t="inlineStr">
@@ -55699,17 +55699,17 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -55727,7 +55727,7 @@
       </c>
       <c r="AQ313" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR313" t="inlineStr">
@@ -55737,7 +55737,7 @@
       </c>
       <c r="AS313" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT313" t="n">
@@ -55745,45 +55745,448 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>2</v>
+      </c>
+      <c r="O314" t="n">
+        <v>2</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU314" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV313" t="inlineStr">
+      <c r="AV314" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW313" t="inlineStr">
+      <c r="AW314" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX313" t="inlineStr">
+      <c r="AX314" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY313" t="inlineStr">
+      <c r="AY314" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ313" t="inlineStr">
+      <c r="AZ314" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA313" t="inlineStr">
+      <c r="BA314" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB313" t="inlineStr">
+      <c r="BB314" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC313" t="inlineStr">
+      <c r="BC314" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>2</v>
+      </c>
+      <c r="O315" t="n">
+        <v>2</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN315" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -55905,7 +56308,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
@@ -55915,7 +56318,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -55935,7 +56338,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -55967,7 +56370,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560514</v>
+        <v>560537</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -55269,12 +55269,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -55299,22 +55299,22 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N311" t="n">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="O311" t="n">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="R311" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.2189046532276254</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -55347,42 +55347,42 @@
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55414,12 +55414,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -55453,100 +55453,81 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O312" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R312" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA312" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR312" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr"/>
       <c r="AT312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -55573,7 +55554,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -55617,103 +55598,28 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O313" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U313" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W313" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X313" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y313" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA313" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB313" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD313" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE313" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF313" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG313" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH313" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI313" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK313" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM313" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN313" t="b">
-        <v>1</v>
       </c>
       <c r="AO313" t="inlineStr">
         <is>
@@ -55812,17 +55718,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -55856,22 +55762,39 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O314" t="n">
-        <v>2</v>
-      </c>
-      <c r="R314" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -55879,6 +55802,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN314" t="b">
+        <v>1</v>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -55891,7 +55872,7 @@
       </c>
       <c r="AQ314" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR314" t="inlineStr">
@@ -55901,7 +55882,7 @@
       </c>
       <c r="AS314" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT314" t="n">
@@ -55909,47 +55890,47 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -55976,7 +55957,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -56025,98 +56006,23 @@
       <c r="O315" t="n">
         <v>2</v>
       </c>
+      <c r="R315" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U315" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA315" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN315" t="b">
-        <v>1</v>
       </c>
       <c r="AO315" t="inlineStr">
         <is>
@@ -56187,6 +56093,245 @@
         </is>
       </c>
       <c r="BC315" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>2</v>
+      </c>
+      <c r="O316" t="n">
+        <v>2</v>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN316" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -56308,7 +56453,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -56318,7 +56463,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -56370,7 +56515,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560537</v>
+        <v>560808</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -44094,13 +44094,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O244" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R244" t="n">
-        <v>0.5619402083865279</v>
+        <v>0.5656130202060476</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -51513,13 +51513,13 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O287" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R287" t="n">
-        <v>0.4480830419814144</v>
+        <v>0.4517558538009342</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -55598,13 +55598,13 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O313" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R313" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -55762,10 +55762,10 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O314" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
@@ -56001,13 +56001,13 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O315" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R315" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -56165,10 +56165,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O316" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560808</v>
+        <v>560815</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -51513,13 +51513,13 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O287" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R287" t="n">
-        <v>0.4517558538009342</v>
+        <v>0.4554286656204539</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -52755,12 +52755,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -52794,100 +52794,84 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>8</v>
+        <v>55082</v>
       </c>
       <c r="O296" t="n">
-        <v>8</v>
+        <v>55082</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>182</v>
       </c>
       <c r="R296" t="n">
-        <v>0.142304733669131</v>
+        <v>3.898467744665</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA296" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ296" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR296" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS296" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr"/>
       <c r="AT296" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -52914,7 +52898,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -52963,98 +52947,23 @@
       <c r="O297" t="n">
         <v>8</v>
       </c>
+      <c r="R297" t="n">
+        <v>0.142304733669131</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U297" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W297" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X297" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y297" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB297" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC297" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD297" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE297" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF297" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG297" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH297" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI297" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ297" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK297" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM297" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN297" t="b">
-        <v>1</v>
       </c>
       <c r="AO297" t="inlineStr">
         <is>
@@ -53153,17 +53062,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -53197,22 +53106,39 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O298" t="n">
-        <v>6</v>
-      </c>
-      <c r="R298" t="n">
-        <v>0.1061385495477304</v>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -53220,6 +53146,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM298" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN298" t="b">
+        <v>1</v>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -53232,7 +53216,7 @@
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR298" t="inlineStr">
@@ -53242,7 +53226,7 @@
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT298" t="n">
@@ -53250,47 +53234,47 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -53317,7 +53301,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -53366,98 +53350,23 @@
       <c r="O299" t="n">
         <v>6</v>
       </c>
+      <c r="R299" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U299" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X299" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y299" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD299" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE299" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG299" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM299" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN299" t="b">
-        <v>1</v>
       </c>
       <c r="AO299" t="inlineStr">
         <is>
@@ -53556,17 +53465,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -53600,22 +53509,39 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O300" t="n">
-        <v>22</v>
-      </c>
-      <c r="R300" t="n">
-        <v>0.2055873694222336</v>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -53623,6 +53549,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN300" t="b">
+        <v>1</v>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -53645,7 +53629,7 @@
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -53658,42 +53642,42 @@
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -53720,7 +53704,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -53769,98 +53753,23 @@
       <c r="O301" t="n">
         <v>22</v>
       </c>
+      <c r="R301" t="n">
+        <v>0.2055873694222336</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U301" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
         </is>
       </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>Tuberkulos</t>
-        </is>
-      </c>
-      <c r="Y301" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA301" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB301" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD301" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE301" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF301" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG301" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ301" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK301" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
-        </is>
-      </c>
-      <c r="AM301" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN301" t="b">
-        <v>1</v>
       </c>
       <c r="AO301" t="inlineStr">
         <is>
@@ -53959,17 +53868,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -54003,81 +53912,175 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="O302" t="n">
-        <v>72</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN302" t="b">
+        <v>1</v>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ302" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR302" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS302" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54109,12 +54112,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -54139,7 +54142,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -54148,13 +54151,13 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="O303" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="R303" t="n">
-        <v>0.2221718868578884</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -54187,42 +54190,42 @@
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54254,12 +54257,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -54284,7 +54287,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -54293,13 +54296,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="O304" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="R304" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -54332,42 +54335,42 @@
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54399,12 +54402,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -54429,7 +54432,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -54438,13 +54441,13 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="O305" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="R305" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -54477,42 +54480,42 @@
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54544,12 +54547,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -54574,7 +54577,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -54583,13 +54586,13 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="O306" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="R306" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.2033852934838758</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -54622,42 +54625,42 @@
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54689,12 +54692,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -54719,7 +54722,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -54728,13 +54731,13 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="O307" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="R307" t="n">
-        <v>0.1511095553996668</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -54767,42 +54770,42 @@
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54834,12 +54837,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -54864,7 +54867,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -54873,13 +54876,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="O308" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="R308" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.1511095553996668</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -54912,42 +54915,42 @@
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54979,12 +54982,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -55009,7 +55012,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -55018,13 +55021,13 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="O309" t="n">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="R309" t="n">
-        <v>0.1960340178157839</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -55057,42 +55060,42 @@
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55124,12 +55127,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -55154,7 +55157,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -55163,13 +55166,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="O310" t="n">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="R310" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.1960340178157839</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -55202,42 +55205,42 @@
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55269,12 +55272,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -55299,7 +55302,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -55308,13 +55311,13 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>268</v>
+        <v>87</v>
       </c>
       <c r="O311" t="n">
-        <v>268</v>
+        <v>87</v>
       </c>
       <c r="R311" t="n">
-        <v>0.2189046532276254</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -55347,42 +55350,42 @@
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55414,12 +55417,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -55444,22 +55447,22 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N312" t="n">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="O312" t="n">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="R312" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.2189046532276254</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -55492,42 +55495,42 @@
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55559,12 +55562,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -55598,100 +55601,81 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O313" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R313" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA313" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO313" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP313" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ313" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR313" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS313" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr"/>
       <c r="AT313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -55718,7 +55702,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -55767,98 +55751,23 @@
       <c r="O314" t="n">
         <v>9</v>
       </c>
+      <c r="R314" t="n">
+        <v>0.1600928253777724</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U314" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA314" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ314" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM314" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN314" t="b">
-        <v>1</v>
       </c>
       <c r="AO314" t="inlineStr">
         <is>
@@ -55957,17 +55866,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -56001,22 +55910,39 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O315" t="n">
-        <v>5</v>
-      </c>
-      <c r="R315" t="n">
-        <v>0.08844879128977531</v>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -56024,6 +55950,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN315" t="b">
+        <v>1</v>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -56036,7 +56020,7 @@
       </c>
       <c r="AQ315" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR315" t="inlineStr">
@@ -56046,7 +56030,7 @@
       </c>
       <c r="AS315" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT315" t="n">
@@ -56054,47 +56038,47 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -56121,7 +56105,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -56170,98 +56154,23 @@
       <c r="O316" t="n">
         <v>5</v>
       </c>
+      <c r="R316" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U316" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA316" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI316" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ316" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM316" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN316" t="b">
-        <v>1</v>
       </c>
       <c r="AO316" t="inlineStr">
         <is>
@@ -56334,6 +56243,390 @@
       <c r="BC316" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>5</v>
+      </c>
+      <c r="O317" t="n">
+        <v>5</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN317" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>72</v>
+      </c>
+      <c r="O318" t="n">
+        <v>72</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0.02062827455593957</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr"/>
+      <c r="AT318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56370,7 +56663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -56453,7 +56746,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -56463,7 +56756,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11">
@@ -56515,7 +56808,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560815</v>
+        <v>615970</v>
       </c>
     </row>
     <row r="16">
@@ -56525,7 +56818,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1191</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8442,10 +8442,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O45" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -37424,10 +37424,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O207" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -37580,10 +37580,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O208" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
@@ -45194,12 +45194,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -45233,84 +45233,92 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>58871</v>
+        <v>70</v>
       </c>
       <c r="O252" t="n">
-        <v>58871</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>190</v>
-      </c>
-      <c r="R252" t="n">
-        <v>4.166636915801409</v>
+        <v>70</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45337,17 +45345,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -45381,14 +45389,39 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>2177</v>
+        <v>70</v>
       </c>
       <c r="O253" t="n">
-        <v>2177</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>70</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -45396,6 +45429,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary active tuberculosis notifications; confirmed cases only, excluding latent tuberculosis infection, and classified by Diagnosis Date.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45403,7 +45494,7 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
@@ -45413,55 +45504,55 @@
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_TUBERCULOSIS; SER_CN_PROV_REPORT_TUBERCULOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45488,17 +45579,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -45532,170 +45623,84 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>2177</v>
+        <v>58871</v>
       </c>
       <c r="O254" t="n">
-        <v>2177</v>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_TUBERCULOSIS</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_TUBERCULOSIS</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>肺结核</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>country:CN-AH:national</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN254" t="b">
-        <v>1</v>
+        <v>58871</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>190</v>
+      </c>
+      <c r="R254" t="n">
+        <v>4.166636915801409</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_TUBERCULOSIS; SER_CN_PROV_REPORT_TUBERCULOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -45727,12 +45732,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -45766,10 +45771,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1680</v>
+        <v>2177</v>
       </c>
       <c r="O255" t="n">
-        <v>1680</v>
+        <v>2177</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -45841,7 +45846,7 @@
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
@@ -45878,12 +45883,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45917,10 +45922,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1680</v>
+        <v>2177</v>
       </c>
       <c r="O256" t="n">
-        <v>1680</v>
+        <v>2177</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
@@ -45964,7 +45969,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN-AH:national</t>
         </is>
       </c>
       <c r="AD256" t="inlineStr">
@@ -46075,7 +46080,7 @@
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
@@ -46112,12 +46117,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -46151,10 +46156,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>5139</v>
+        <v>1680</v>
       </c>
       <c r="O257" t="n">
-        <v>5139</v>
+        <v>1680</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -46226,7 +46231,7 @@
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
@@ -46263,12 +46268,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -46302,10 +46307,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>5139</v>
+        <v>1680</v>
       </c>
       <c r="O258" t="n">
-        <v>5139</v>
+        <v>1680</v>
       </c>
       <c r="U258" t="inlineStr">
         <is>
@@ -46349,7 +46354,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -46460,7 +46465,7 @@
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
@@ -46497,12 +46502,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -46536,10 +46541,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>4114</v>
+        <v>5139</v>
       </c>
       <c r="O259" t="n">
-        <v>4114</v>
+        <v>5139</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -46611,7 +46616,7 @@
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
@@ -46648,12 +46653,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -46687,10 +46692,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>4114</v>
+        <v>5139</v>
       </c>
       <c r="O260" t="n">
-        <v>4114</v>
+        <v>5139</v>
       </c>
       <c r="U260" t="inlineStr">
         <is>
@@ -46734,7 +46739,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr">
@@ -46845,7 +46850,7 @@
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
@@ -46882,12 +46887,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -46921,10 +46926,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1972</v>
+        <v>4114</v>
       </c>
       <c r="O261" t="n">
-        <v>1972</v>
+        <v>4114</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -46996,7 +47001,7 @@
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
@@ -47033,12 +47038,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -47072,10 +47077,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>1972</v>
+        <v>4114</v>
       </c>
       <c r="O262" t="n">
-        <v>1972</v>
+        <v>4114</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -47119,7 +47124,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
@@ -47230,7 +47235,7 @@
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
@@ -47267,12 +47272,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -47306,10 +47311,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>1584</v>
+        <v>1972</v>
       </c>
       <c r="O263" t="n">
-        <v>1584</v>
+        <v>1972</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -47381,7 +47386,7 @@
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
@@ -47418,12 +47423,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -47457,10 +47462,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>1584</v>
+        <v>1972</v>
       </c>
       <c r="O264" t="n">
-        <v>1584</v>
+        <v>1972</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
@@ -47504,7 +47509,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD264" t="inlineStr">
@@ -47615,7 +47620,7 @@
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
@@ -47652,12 +47657,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -47691,10 +47696,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>4654</v>
+        <v>1584</v>
       </c>
       <c r="O265" t="n">
-        <v>4654</v>
+        <v>1584</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -47766,7 +47771,7 @@
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
@@ -47803,12 +47808,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -47842,10 +47847,10 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>4654</v>
+        <v>1584</v>
       </c>
       <c r="O266" t="n">
-        <v>4654</v>
+        <v>1584</v>
       </c>
       <c r="U266" t="inlineStr">
         <is>
@@ -47889,7 +47894,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -48000,7 +48005,7 @@
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
@@ -48037,12 +48042,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -48076,10 +48081,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>531</v>
+        <v>4654</v>
       </c>
       <c r="O267" t="n">
-        <v>531</v>
+        <v>4654</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -48151,7 +48156,7 @@
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
@@ -48188,12 +48193,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -48227,10 +48232,10 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>531</v>
+        <v>4654</v>
       </c>
       <c r="O268" t="n">
-        <v>531</v>
+        <v>4654</v>
       </c>
       <c r="U268" t="inlineStr">
         <is>
@@ -48274,7 +48279,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr">
@@ -48385,7 +48390,7 @@
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
@@ -48422,12 +48427,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -48461,22 +48466,14 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>13</v>
+        <v>531</v>
       </c>
       <c r="O269" t="n">
-        <v>13</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0.2312451922123379</v>
+        <v>531</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -48491,22 +48488,17 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>SER_CN_PROV_DC_TUBERCULOSIS; SER_CN_PROV_REPORT_TUBERCULOSIS</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -48514,47 +48506,47 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48586,12 +48578,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -48625,29 +48617,29 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>13</v>
+        <v>531</v>
       </c>
       <c r="O270" t="n">
-        <v>13</v>
+        <v>531</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>SER_CN_PROV_REPORT_TUBERCULOSIS</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>SER_CN_PROV_REPORT_TUBERCULOSIS</t>
         </is>
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X270" t="inlineStr">
         <is>
-          <t>Tuberculosis, total</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="Y270" t="inlineStr">
@@ -48657,7 +48649,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -48672,7 +48664,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -48707,17 +48699,17 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -48730,22 +48722,17 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>SER_CN_PROV_DC_TUBERCULOSIS; SER_CN_PROV_REPORT_TUBERCULOSIS</t>
         </is>
       </c>
       <c r="AT270" t="n">
@@ -48753,47 +48740,47 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48825,12 +48812,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -48864,81 +48851,100 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="O271" t="n">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="R271" t="n">
-        <v>3.78120408174882</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48965,17 +48971,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -49009,22 +49015,39 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O272" t="n">
-        <v>6</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0.1061385495477304</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -49032,6 +49055,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -49044,7 +49125,7 @@
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
@@ -49054,7 +49135,7 @@
       </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -49062,47 +49143,47 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -49129,17 +49210,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -49173,175 +49254,81 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>6</v>
+        <v>279</v>
       </c>
       <c r="O273" t="n">
-        <v>6</v>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN273" t="b">
-        <v>1</v>
+        <v>279</v>
+      </c>
+      <c r="R273" t="n">
+        <v>3.78120408174882</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR273" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -49373,12 +49360,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -49412,13 +49399,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="O274" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="R274" t="n">
-        <v>0.6619411632651402</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -49427,7 +49414,7 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -49442,7 +49429,7 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ274" t="inlineStr">
@@ -49450,57 +49437,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS274" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49532,12 +49524,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -49571,29 +49563,29 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="O275" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X275" t="inlineStr">
         <is>
-          <t>Tuberculosis disease</t>
+          <t>Tuberkulose</t>
         </is>
       </c>
       <c r="Y275" t="inlineStr">
@@ -49603,7 +49595,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -49618,7 +49610,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -49653,17 +49645,17 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
         </is>
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -49676,7 +49668,7 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ275" t="inlineStr">
@@ -49684,57 +49676,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49766,12 +49763,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -49805,13 +49802,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O276" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R276" t="n">
-        <v>0.242966891135367</v>
+        <v>0.6619411632651402</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -49820,7 +49817,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -49835,7 +49832,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ276" t="inlineStr">
@@ -49843,62 +49840,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR276" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49930,12 +49922,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -49969,29 +49961,29 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O277" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X277" t="inlineStr">
         <is>
-          <t>Tuberkulos</t>
+          <t>Tuberculosis disease</t>
         </is>
       </c>
       <c r="Y277" t="inlineStr">
@@ -50001,7 +49993,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -50016,7 +50008,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -50051,17 +50043,17 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
         </is>
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -50074,7 +50066,7 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ277" t="inlineStr">
@@ -50082,62 +50074,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50169,12 +50156,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -50199,7 +50186,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -50208,81 +50195,100 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="O278" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="R278" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.242966891135367</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -50309,17 +50315,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -50344,7 +50350,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -50353,81 +50359,175 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="O279" t="n">
-        <v>62</v>
-      </c>
-      <c r="R279" t="n">
-        <v>0.01776323642317019</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -50489,7 +50589,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -50498,13 +50598,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="O280" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="R280" t="n">
-        <v>0.1894995505552578</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -50634,7 +50734,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -50643,13 +50743,13 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="O281" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="R281" t="n">
-        <v>0.03237493090029405</v>
+        <v>0.01776323642317019</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -50779,7 +50879,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -50788,13 +50888,13 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="O282" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="R282" t="n">
-        <v>0.2017516766687443</v>
+        <v>0.1894995505552578</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -50924,7 +51024,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -50933,13 +51033,13 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="O283" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="R283" t="n">
-        <v>0.01833624404972407</v>
+        <v>0.03237493090029405</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -51069,7 +51169,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -51078,13 +51178,13 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O284" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="R284" t="n">
-        <v>0.199301251446047</v>
+        <v>0.2017516766687443</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -51214,7 +51314,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -51223,13 +51323,13 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="O285" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="R285" t="n">
-        <v>0.02148778599577039</v>
+        <v>0.01833624404972407</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -51359,7 +51459,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -51368,13 +51468,13 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="O286" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="R286" t="n">
-        <v>0.1837818917022974</v>
+        <v>0.199301251446047</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -51474,12 +51574,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -51504,22 +51604,22 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N287" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="O287" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="R287" t="n">
-        <v>0.4554286656204539</v>
+        <v>0.02148778599577039</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -51552,42 +51652,42 @@
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -51619,12 +51719,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -51649,23 +51749,26 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="O288" t="n">
-        <v>0</v>
+        <v>225</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0.1837818917022974</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -51694,42 +51797,42 @@
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51761,12 +51864,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -51800,14 +51903,17 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="O289" t="n">
-        <v>50</v>
+        <v>124</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.4554286656204539</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
@@ -51841,12 +51947,12 @@
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -51861,12 +51967,12 @@
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC289" t="inlineStr">
@@ -51903,12 +52009,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -51942,10 +52048,10 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -51983,7 +52089,7 @@
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
@@ -52003,7 +52109,7 @@
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
@@ -52045,12 +52151,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -52084,10 +52190,10 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O291" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
@@ -52125,7 +52231,7 @@
       </c>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
@@ -52145,7 +52251,7 @@
       </c>
       <c r="BA291" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB291" t="inlineStr">
@@ -52187,12 +52293,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -52226,10 +52332,10 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O292" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -52267,7 +52373,7 @@
       </c>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
@@ -52287,7 +52393,7 @@
       </c>
       <c r="BA292" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB292" t="inlineStr">
@@ -52329,12 +52435,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -52368,10 +52474,10 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O293" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
@@ -52409,7 +52515,7 @@
       </c>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
@@ -52429,7 +52535,7 @@
       </c>
       <c r="BA293" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB293" t="inlineStr">
@@ -52471,12 +52577,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -52510,10 +52616,10 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O294" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -52551,7 +52657,7 @@
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
@@ -52571,7 +52677,7 @@
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
@@ -52613,12 +52719,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -52652,10 +52758,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S295" t="inlineStr">
         <is>
@@ -52693,7 +52799,7 @@
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
@@ -52713,7 +52819,7 @@
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
@@ -52755,12 +52861,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -52794,20 +52900,14 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>55082</v>
+        <v>17</v>
       </c>
       <c r="O296" t="n">
-        <v>55082</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>182</v>
-      </c>
-      <c r="R296" t="n">
-        <v>3.898467744665</v>
+        <v>17</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -52836,42 +52936,42 @@
       </c>
       <c r="AV296" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -52903,12 +53003,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -52942,100 +53042,78 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O297" t="n">
-        <v>8</v>
-      </c>
-      <c r="R297" t="n">
-        <v>0.142304733669131</v>
+        <v>14</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA297" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ297" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR297" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS297" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr"/>
       <c r="AT297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53062,17 +53140,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -53106,175 +53184,84 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>8</v>
+        <v>55082</v>
       </c>
       <c r="O298" t="n">
-        <v>8</v>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V298" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W298" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X298" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y298" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z298" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA298" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB298" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC298" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD298" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE298" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF298" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG298" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH298" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI298" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ298" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK298" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM298" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN298" t="b">
-        <v>1</v>
+        <v>55082</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>182</v>
+      </c>
+      <c r="R298" t="n">
+        <v>3.898467744665</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ298" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR298" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS298" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr"/>
       <c r="AT298" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -53306,12 +53293,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -53345,13 +53332,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O299" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R299" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
@@ -53360,7 +53347,7 @@
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -53380,7 +53367,7 @@
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR299" t="inlineStr">
@@ -53390,7 +53377,7 @@
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT299" t="n">
@@ -53398,47 +53385,47 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -53470,12 +53457,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -53509,29 +53496,29 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O300" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X300" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y300" t="inlineStr">
@@ -53556,7 +53543,7 @@
       </c>
       <c r="AC300" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD300" t="inlineStr">
@@ -53591,17 +53578,17 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -53619,7 +53606,7 @@
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR300" t="inlineStr">
@@ -53629,7 +53616,7 @@
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -53637,47 +53624,47 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -53709,12 +53696,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -53748,13 +53735,13 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O301" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="R301" t="n">
-        <v>0.2055873694222336</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
@@ -53763,7 +53750,7 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -53793,7 +53780,7 @@
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT301" t="n">
@@ -53806,42 +53793,42 @@
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -53873,12 +53860,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -53912,29 +53899,29 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O302" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X302" t="inlineStr">
         <is>
-          <t>Tuberkulos</t>
+          <t>Tuberkulose</t>
         </is>
       </c>
       <c r="Y302" t="inlineStr">
@@ -53959,7 +53946,7 @@
       </c>
       <c r="AC302" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD302" t="inlineStr">
@@ -53994,17 +53981,17 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
         </is>
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -54032,7 +54019,7 @@
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT302" t="n">
@@ -54045,42 +54032,42 @@
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -54112,12 +54099,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -54151,81 +54138,100 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="O303" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="R303" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ303" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR303" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS303" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54252,17 +54258,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -54287,7 +54293,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -54296,81 +54302,175 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>272</v>
+        <v>22</v>
       </c>
       <c r="O304" t="n">
-        <v>272</v>
-      </c>
-      <c r="R304" t="n">
-        <v>0.2221718868578884</v>
-      </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ304" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK304" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM304" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN304" t="b">
+        <v>1</v>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ304" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR304" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS304" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT304" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54532,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -54441,13 +54541,13 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="O305" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R305" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -54577,7 +54677,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -54586,13 +54686,13 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="O306" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="R306" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -54722,7 +54822,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -54731,13 +54831,13 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="O307" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="R307" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -54867,7 +54967,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -54876,13 +54976,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="O308" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="R308" t="n">
-        <v>0.1511095553996668</v>
+        <v>0.2033852934838758</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -55012,7 +55112,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -55021,13 +55121,13 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O309" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="R309" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -55157,7 +55257,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -55166,13 +55266,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="O310" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="R310" t="n">
-        <v>0.1960340178157839</v>
+        <v>0.1511095553996668</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -55302,7 +55402,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -55311,13 +55411,13 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="O311" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="R311" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -55447,7 +55547,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -55456,13 +55556,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="O312" t="n">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="R312" t="n">
-        <v>0.2189046532276254</v>
+        <v>0.1960340178157839</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -55562,12 +55662,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -55592,22 +55692,22 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N313" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="O313" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="R313" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -55640,42 +55740,42 @@
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55707,12 +55807,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -55737,109 +55837,90 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N314" t="n">
-        <v>9</v>
+        <v>268</v>
       </c>
       <c r="O314" t="n">
-        <v>9</v>
+        <v>268</v>
       </c>
       <c r="R314" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.2189046532276254</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO314" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ314" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR314" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS314" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr"/>
       <c r="AT314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55866,17 +55947,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -55910,175 +55991,81 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O315" t="n">
-        <v>9</v>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0.04407374183423748</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr"/>
+      <c r="AT315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN315" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO315" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ315" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR315" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AT315" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU315" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV315" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -56110,12 +56097,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -56149,13 +56136,13 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O316" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R316" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -56164,7 +56151,7 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -56184,7 +56171,7 @@
       </c>
       <c r="AQ316" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR316" t="inlineStr">
@@ -56194,7 +56181,7 @@
       </c>
       <c r="AS316" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT316" t="n">
@@ -56202,47 +56189,47 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -56274,12 +56261,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -56313,29 +56300,29 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O317" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y317" t="inlineStr">
@@ -56360,7 +56347,7 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD317" t="inlineStr">
@@ -56395,17 +56382,17 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -56423,7 +56410,7 @@
       </c>
       <c r="AQ317" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR317" t="inlineStr">
@@ -56433,7 +56420,7 @@
       </c>
       <c r="AS317" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT317" t="n">
@@ -56441,47 +56428,47 @@
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -56513,118 +56500,521 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>5</v>
+      </c>
+      <c r="O318" t="n">
+        <v>5</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>5</v>
+      </c>
+      <c r="O319" t="n">
+        <v>5</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN319" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
+      <c r="G320" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>D025</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
         <is>
           <t>肺结核</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
+      <c r="K320" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="L320" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
+      <c r="M320" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N318" t="n">
+      <c r="N320" t="n">
         <v>72</v>
       </c>
-      <c r="O318" t="n">
+      <c r="O320" t="n">
         <v>72</v>
       </c>
-      <c r="R318" t="n">
+      <c r="R320" t="n">
         <v>0.02062827455593957</v>
       </c>
-      <c r="S318" t="inlineStr">
+      <c r="S320" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO318" t="inlineStr">
+      <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP318" t="inlineStr">
+      <c r="AP320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR318" t="inlineStr">
+      <c r="AR320" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS318" t="inlineStr"/>
-      <c r="AT318" t="n">
+      <c r="AS320" t="inlineStr"/>
+      <c r="AT320" t="n">
         <v>0</v>
       </c>
-      <c r="AU318" t="inlineStr">
+      <c r="AU320" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV318" t="inlineStr">
+      <c r="AV320" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW318" t="inlineStr">
+      <c r="AW320" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX318" t="inlineStr">
+      <c r="AX320" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY318" t="inlineStr">
+      <c r="AY320" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ318" t="inlineStr">
+      <c r="AZ320" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA318" t="inlineStr">
+      <c r="BA320" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB318" t="inlineStr">
+      <c r="BB320" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC318" t="inlineStr">
+      <c r="BC320" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -56746,7 +57136,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -56756,7 +57146,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11">
@@ -56776,7 +57166,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -56808,7 +57198,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>615970</v>
+        <v>616042</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -44094,13 +44094,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O244" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R244" t="n">
-        <v>0.5656130202060476</v>
+        <v>0.5619402083865279</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -51903,13 +51903,13 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O289" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R289" t="n">
-        <v>0.4554286656204539</v>
+        <v>0.4480830419814144</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616042</v>
+        <v>616039</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -57020,6 +57020,151 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>257</v>
+      </c>
+      <c r="O321" t="n">
+        <v>257</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0.2099197607444019</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr"/>
+      <c r="AT321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -57053,7 +57198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -57136,7 +57281,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -57146,7 +57291,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
@@ -57198,7 +57343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616039</v>
+        <v>616296</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -54099,12 +54099,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -54138,13 +54138,13 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O303" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="R303" t="n">
-        <v>0.2055873694222336</v>
+        <v>0.7565041865887316</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -54168,7 +54168,7 @@
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ303" t="inlineStr">
@@ -54176,62 +54176,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR303" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54263,12 +54258,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -54302,29 +54297,29 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O304" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W304" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X304" t="inlineStr">
         <is>
-          <t>Tuberkulos</t>
+          <t>Tuberculosis disease</t>
         </is>
       </c>
       <c r="Y304" t="inlineStr">
@@ -54334,7 +54329,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -54349,7 +54344,7 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD304" t="inlineStr">
@@ -54384,17 +54379,17 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
         </is>
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -54407,7 +54402,7 @@
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ304" t="inlineStr">
@@ -54415,62 +54410,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR304" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54502,12 +54492,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -54541,81 +54531,100 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="O305" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="R305" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ305" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR305" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS305" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT305" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54642,17 +54651,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -54677,7 +54686,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -54686,81 +54695,175 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>272</v>
+        <v>22</v>
       </c>
       <c r="O306" t="n">
-        <v>272</v>
-      </c>
-      <c r="R306" t="n">
-        <v>0.2221718868578884</v>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ306" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK306" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM306" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN306" t="b">
+        <v>1</v>
       </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ306" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR306" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS306" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54822,7 +54925,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -54831,13 +54934,13 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="O307" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R307" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -54967,7 +55070,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -54976,13 +55079,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="O308" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="R308" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -55112,7 +55215,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -55121,13 +55224,13 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="O309" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="R309" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -55257,7 +55360,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -55266,13 +55369,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="O310" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="R310" t="n">
-        <v>0.1511095553996668</v>
+        <v>0.2033852934838758</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -55402,7 +55505,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -55411,13 +55514,13 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O311" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="R311" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -55547,7 +55650,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -55556,13 +55659,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="O312" t="n">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="R312" t="n">
-        <v>0.1960340178157839</v>
+        <v>0.1511095553996668</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -55692,7 +55795,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -55701,13 +55804,13 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="O313" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="R313" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -55837,7 +55940,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -55846,13 +55949,13 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="O314" t="n">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="R314" t="n">
-        <v>0.2189046532276254</v>
+        <v>0.1960340178157839</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -55952,12 +56055,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -55982,22 +56085,22 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N315" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="O315" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="R315" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -56030,42 +56133,42 @@
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56097,12 +56200,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -56127,109 +56230,90 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N316" t="n">
-        <v>9</v>
+        <v>268</v>
       </c>
       <c r="O316" t="n">
-        <v>9</v>
+        <v>268</v>
       </c>
       <c r="R316" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.2189046532276254</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR316" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
       <c r="AT316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56256,17 +56340,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -56300,175 +56384,81 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O317" t="n">
-        <v>9</v>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0.04407374183423748</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr"/>
+      <c r="AT317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN317" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO317" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP317" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ317" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR317" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AT317" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU317" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV317" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -56500,12 +56490,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -56539,13 +56529,13 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O318" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R318" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -56554,7 +56544,7 @@
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -56574,7 +56564,7 @@
       </c>
       <c r="AQ318" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR318" t="inlineStr">
@@ -56584,7 +56574,7 @@
       </c>
       <c r="AS318" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT318" t="n">
@@ -56592,47 +56582,47 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -56664,12 +56654,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -56703,29 +56693,29 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O319" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X319" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y319" t="inlineStr">
@@ -56750,7 +56740,7 @@
       </c>
       <c r="AC319" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD319" t="inlineStr">
@@ -56785,17 +56775,17 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -56813,7 +56803,7 @@
       </c>
       <c r="AQ319" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR319" t="inlineStr">
@@ -56823,7 +56813,7 @@
       </c>
       <c r="AS319" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT319" t="n">
@@ -56831,47 +56821,47 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV319" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA319" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB319" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC319" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -56903,12 +56893,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -56933,7 +56923,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -56942,81 +56932,100 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="O320" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="R320" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR320" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS320" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -57043,123 +57052,507 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>5</v>
+      </c>
+      <c r="O321" t="n">
+        <v>5</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN321" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>72</v>
+      </c>
+      <c r="O322" t="n">
+        <v>72</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0.02062827455593957</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
+      <c r="AT322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
+      <c r="G323" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>D025</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>Tuberculosis</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
         <is>
           <t>肺结核</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="K323" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
+      <c r="L323" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="M323" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N321" t="n">
+      <c r="N323" t="n">
         <v>257</v>
       </c>
-      <c r="O321" t="n">
+      <c r="O323" t="n">
         <v>257</v>
       </c>
-      <c r="R321" t="n">
+      <c r="R323" t="n">
         <v>0.2099197607444019</v>
       </c>
-      <c r="S321" t="inlineStr">
+      <c r="S323" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO321" t="inlineStr">
+      <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP321" t="inlineStr">
+      <c r="AP323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR321" t="inlineStr">
+      <c r="AR323" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS321" t="inlineStr"/>
-      <c r="AT321" t="n">
+      <c r="AS323" t="inlineStr"/>
+      <c r="AT323" t="n">
         <v>0</v>
       </c>
-      <c r="AU321" t="inlineStr">
+      <c r="AU323" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV321" t="inlineStr">
+      <c r="AV323" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW321" t="inlineStr">
+      <c r="AW323" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX321" t="inlineStr">
+      <c r="AX323" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY321" t="inlineStr">
+      <c r="AY323" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ321" t="inlineStr">
+      <c r="AZ323" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA321" t="inlineStr">
+      <c r="BA323" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB321" t="inlineStr">
+      <c r="BB323" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC321" t="inlineStr">
+      <c r="BC323" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -57281,7 +57674,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -57291,7 +57684,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -57311,7 +57704,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -57343,7 +57736,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616296</v>
+        <v>616336</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -54531,13 +54531,13 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O305" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R305" t="n">
-        <v>0.2055873694222336</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -54695,10 +54695,10 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O306" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U306" t="inlineStr">
         <is>
@@ -56932,13 +56932,13 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O320" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R320" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
@@ -57096,10 +57096,10 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O321" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616336</v>
+        <v>616339</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -56529,13 +56529,13 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O318" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R318" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -56693,10 +56693,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O319" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616339</v>
+        <v>616341</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -44094,13 +44094,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O244" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="R244" t="n">
-        <v>0.5619402083865279</v>
+        <v>0.5803042674841269</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -51903,13 +51903,13 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="O289" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="R289" t="n">
-        <v>0.4480830419814144</v>
+        <v>0.4811383483570925</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -57555,6 +57555,151 @@
       <c r="BC323" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>66</v>
+      </c>
+      <c r="O324" t="n">
+        <v>66</v>
+      </c>
+      <c r="R324" t="n">
+        <v>0.01890925167627794</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr"/>
+      <c r="AT324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV324" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -57591,7 +57736,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -57674,7 +57819,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -57684,7 +57829,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -57736,7 +57881,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616341</v>
+        <v>616421</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -51903,13 +51903,13 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O289" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R289" t="n">
-        <v>0.4811383483570925</v>
+        <v>0.4774655365375727</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616421</v>
+        <v>616420</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -51903,13 +51903,13 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O289" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R289" t="n">
-        <v>0.4774655365375727</v>
+        <v>0.4701199128985332</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -53332,13 +53332,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O299" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R299" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
@@ -53496,10 +53496,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O300" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
@@ -53696,12 +53696,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -53735,100 +53735,81 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>6</v>
+        <v>227</v>
       </c>
       <c r="O301" t="n">
-        <v>6</v>
+        <v>227</v>
       </c>
       <c r="R301" t="n">
-        <v>0.1061385495477304</v>
+        <v>3.07646353604653</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA301" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ301" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR301" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS301" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr"/>
       <c r="AT301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -53855,7 +53836,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -53904,98 +53885,23 @@
       <c r="O302" t="n">
         <v>6</v>
       </c>
+      <c r="R302" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U302" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X302" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y302" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD302" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE302" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF302" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG302" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH302" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI302" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ302" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK302" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM302" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN302" t="b">
-        <v>1</v>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
@@ -54094,17 +54000,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -54138,22 +54044,39 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="O303" t="n">
-        <v>40</v>
-      </c>
-      <c r="R303" t="n">
-        <v>0.7565041865887316</v>
-      </c>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -54161,6 +54084,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM303" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN303" t="b">
+        <v>1</v>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -54168,7 +54149,7 @@
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ303" t="inlineStr">
@@ -54176,57 +54157,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -54253,7 +54239,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -54302,98 +54288,23 @@
       <c r="O304" t="n">
         <v>40</v>
       </c>
+      <c r="R304" t="n">
+        <v>0.7565041865887316</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U304" t="inlineStr">
         <is>
           <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W304" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X304" t="inlineStr">
-        <is>
-          <t>Tuberculosis disease</t>
-        </is>
-      </c>
-      <c r="Y304" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB304" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD304" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE304" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF304" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG304" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH304" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI304" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ304" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK304" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM304" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN304" t="b">
-        <v>1</v>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
@@ -54487,17 +54398,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -54531,22 +54442,39 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="O305" t="n">
-        <v>23</v>
-      </c>
-      <c r="R305" t="n">
-        <v>0.214932249850517</v>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>40</v>
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Tuberculosis disease</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -54554,6 +54482,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN305" t="b">
+        <v>1</v>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -54561,7 +54547,7 @@
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ305" t="inlineStr">
@@ -54569,62 +54555,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR305" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54651,7 +54632,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -54695,103 +54676,28 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O306" t="n">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0.2055873694222336</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U306" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
         </is>
       </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
-        </is>
-      </c>
-      <c r="W306" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X306" t="inlineStr">
-        <is>
-          <t>Tuberkulos</t>
-        </is>
-      </c>
-      <c r="Y306" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA306" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB306" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC306" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD306" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE306" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF306" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG306" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ306" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK306" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
-        </is>
-      </c>
-      <c r="AM306" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN306" t="b">
-        <v>1</v>
       </c>
       <c r="AO306" t="inlineStr">
         <is>
@@ -54890,17 +54796,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -54934,81 +54840,175 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="O307" t="n">
-        <v>72</v>
-      </c>
-      <c r="R307" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK307" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM307" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN307" t="b">
+        <v>1</v>
       </c>
       <c r="AO307" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP307" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ307" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR307" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS307" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS307" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55040,12 +55040,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -55070,7 +55070,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -55079,13 +55079,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="O308" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="R308" t="n">
-        <v>0.2221718868578884</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -55118,42 +55118,42 @@
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55185,12 +55185,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -55215,7 +55215,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -55224,13 +55224,13 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="O309" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="R309" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -55263,42 +55263,42 @@
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55330,12 +55330,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -55360,7 +55360,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -55369,13 +55369,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="O310" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="R310" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -55408,42 +55408,42 @@
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55475,12 +55475,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -55505,7 +55505,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -55514,13 +55514,13 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="O311" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="R311" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.2033852934838758</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -55553,42 +55553,42 @@
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55620,12 +55620,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -55650,7 +55650,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -55659,13 +55659,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="O312" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="R312" t="n">
-        <v>0.1511095553996668</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -55698,42 +55698,42 @@
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55765,12 +55765,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -55795,7 +55795,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -55804,13 +55804,13 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="O313" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="R313" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.1511095553996668</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -55843,42 +55843,42 @@
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55910,12 +55910,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -55940,7 +55940,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -55949,13 +55949,13 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="O314" t="n">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="R314" t="n">
-        <v>0.1960340178157839</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -55988,42 +55988,42 @@
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56055,12 +56055,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -56085,7 +56085,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -56094,13 +56094,13 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="O315" t="n">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="R315" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.1960340178157839</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -56133,42 +56133,42 @@
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56200,12 +56200,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -56230,7 +56230,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -56239,13 +56239,13 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>268</v>
+        <v>87</v>
       </c>
       <c r="O316" t="n">
-        <v>268</v>
+        <v>87</v>
       </c>
       <c r="R316" t="n">
-        <v>0.2189046532276254</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -56278,42 +56278,42 @@
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56345,12 +56345,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -56375,22 +56375,22 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N317" t="n">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="O317" t="n">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="R317" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.2189046532276254</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -56423,42 +56423,42 @@
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56490,12 +56490,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -56529,100 +56529,81 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O318" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R318" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA318" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO318" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ318" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR318" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS318" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr"/>
       <c r="AT318" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -56649,7 +56630,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -56693,103 +56674,28 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O319" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U319" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ319" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM319" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN319" t="b">
-        <v>1</v>
       </c>
       <c r="AO319" t="inlineStr">
         <is>
@@ -56888,17 +56794,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -56932,22 +56838,39 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O320" t="n">
-        <v>7</v>
-      </c>
-      <c r="R320" t="n">
-        <v>0.1238283078056854</v>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -56955,6 +56878,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN320" t="b">
+        <v>1</v>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -56967,7 +56948,7 @@
       </c>
       <c r="AQ320" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR320" t="inlineStr">
@@ -56977,7 +56958,7 @@
       </c>
       <c r="AS320" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT320" t="n">
@@ -56985,47 +56966,47 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -57052,7 +57033,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -57101,98 +57082,23 @@
       <c r="O321" t="n">
         <v>7</v>
       </c>
+      <c r="R321" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U321" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W321" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X321" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y321" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB321" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD321" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE321" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF321" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG321" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ321" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK321" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM321" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN321" t="b">
-        <v>1</v>
       </c>
       <c r="AO321" t="inlineStr">
         <is>
@@ -57291,17 +57197,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -57326,7 +57232,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -57335,81 +57241,175 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="O322" t="n">
-        <v>72</v>
-      </c>
-      <c r="R322" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK322" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM322" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN322" t="b">
+        <v>1</v>
       </c>
       <c r="AO322" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR322" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS322" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT322" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -57441,12 +57441,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -57471,7 +57471,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -57480,13 +57480,13 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>257</v>
+        <v>72</v>
       </c>
       <c r="O323" t="n">
-        <v>257</v>
+        <v>72</v>
       </c>
       <c r="R323" t="n">
-        <v>0.2099197607444019</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S323" t="inlineStr">
         <is>
@@ -57519,42 +57519,42 @@
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -57586,12 +57586,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -57616,7 +57616,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -57625,13 +57625,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="O324" t="n">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="R324" t="n">
-        <v>0.01890925167627794</v>
+        <v>0.2099197607444019</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -57664,40 +57664,475 @@
       </c>
       <c r="AV324" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>66</v>
+      </c>
+      <c r="O325" t="n">
+        <v>66</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0.01890925167627794</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr"/>
+      <c r="AT325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW324" t="inlineStr">
+      <c r="AW325" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX324" t="inlineStr">
+      <c r="AX325" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY324" t="inlineStr">
+      <c r="AY325" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ324" t="inlineStr">
+      <c r="AZ325" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA324" t="inlineStr">
+      <c r="BA325" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB324" t="inlineStr">
+      <c r="BB325" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC324" t="inlineStr">
+      <c r="BC325" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>265</v>
+      </c>
+      <c r="O326" t="n">
+        <v>265</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0.2164542280049281</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR326" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr"/>
+      <c r="AT326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>56</v>
+      </c>
+      <c r="O327" t="n">
+        <v>56</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0.01604421354350856</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR327" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr"/>
+      <c r="AT327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -57736,7 +58171,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -57819,7 +58254,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
@@ -57829,7 +58264,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11">
@@ -57881,7 +58316,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>616420</v>
+        <v>616969</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -59609,13 +59609,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="O334" t="n">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="R334" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.5362305256498894</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
@@ -59754,13 +59754,13 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O335" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R335" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -59918,10 +59918,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O336" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U336" t="inlineStr">
         <is>
@@ -61215,6 +61215,699 @@
       <c r="BC343" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>261</v>
+      </c>
+      <c r="O344" t="n">
+        <v>261</v>
+      </c>
+      <c r="R344" t="n">
+        <v>0.213186994374665</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO344" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP344" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr"/>
+      <c r="AT344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV344" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW344" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX344" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY344" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA344" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB344" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC344" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>82</v>
+      </c>
+      <c r="O345" t="n">
+        <v>82</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0.02349331268870896</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO345" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP345" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr"/>
+      <c r="AT345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV345" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW345" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX345" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY345" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA345" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB345" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC345" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>0</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>0</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO346" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP346" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ346" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="AT346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU346" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV346" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW346" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX346" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY346" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA346" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB346" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC346" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF347" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ347" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK347" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM347" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN347" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ347" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="AT347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV347" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW347" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX347" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY347" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA347" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB347" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC347" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -61251,7 +61944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -61334,7 +62027,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -61344,7 +62037,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -61364,7 +62057,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
@@ -61396,7 +62089,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>637371</v>
+        <v>637852</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -52288,13 +52288,13 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O291" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R291" t="n">
-        <v>0.4701199128985332</v>
+        <v>0.4627742892594935</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
@@ -59609,13 +59609,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O334" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R334" t="n">
-        <v>0.5362305256498894</v>
+        <v>0.5435761492889289</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -5860,7 +5860,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -34149,7 +34149,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -41991,7 +41991,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -50040,7 +50040,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -56960,13 +56960,13 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O318" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R318" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -57124,10 +57124,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O319" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
@@ -57216,7 +57216,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -59754,13 +59754,13 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O335" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R335" t="n">
-        <v>0.3023975590469034</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -59918,10 +59918,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O336" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U336" t="inlineStr">
         <is>
@@ -60157,13 +60157,13 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O337" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R337" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
@@ -60321,10 +60321,10 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O338" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U338" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN338" t="b">
@@ -61575,13 +61575,13 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R346" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S346" t="inlineStr">
         <is>
@@ -61739,10 +61739,10 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U347" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>637852</v>
+        <v>637858</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -74441,13 +74441,13 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O444" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R444" t="n">
-        <v>0.4517558538009342</v>
+        <v>0.4480830419814144</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -83579,13 +83579,13 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O498" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R498" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S498" t="inlineStr">
         <is>
@@ -83743,10 +83743,10 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O499" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U499" t="inlineStr">
         <is>
@@ -85968,13 +85968,13 @@
         </is>
       </c>
       <c r="N512" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O512" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R512" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S512" t="inlineStr">
         <is>
@@ -86132,10 +86132,10 @@
         </is>
       </c>
       <c r="N513" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O513" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U513" t="inlineStr">
         <is>
@@ -87035,7 +87035,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>640629</v>
+        <v>640634</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -74441,13 +74441,13 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O444" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="R444" t="n">
-        <v>0.4480830419814144</v>
+        <v>0.4591014774399738</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -80378,13 +80378,13 @@
         </is>
       </c>
       <c r="N477" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O477" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R477" t="n">
-        <v>0.2055873694222336</v>
+        <v>0.1962424889939503</v>
       </c>
       <c r="S477" t="inlineStr">
         <is>
@@ -80542,10 +80542,10 @@
         </is>
       </c>
       <c r="N478" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O478" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U478" t="inlineStr">
         <is>
@@ -82256,13 +82256,13 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="O489" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="R489" t="n">
-        <v>0.5582673965670081</v>
+        <v>0.594995514762206</v>
       </c>
       <c r="S489" t="inlineStr">
         <is>
@@ -84385,13 +84385,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O502" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R502" t="n">
-        <v>0.1962424889939503</v>
+        <v>0.1868976085656669</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -84549,10 +84549,10 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O503" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
@@ -86371,13 +86371,13 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O514" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R514" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -86535,10 +86535,10 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U515" t="inlineStr">
         <is>
@@ -86854,6 +86854,151 @@
       <c r="BC516" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N517" t="n">
+        <v>261</v>
+      </c>
+      <c r="O517" t="n">
+        <v>261</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0.213186994374665</v>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO517" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP517" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR517" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS517" t="inlineStr"/>
+      <c r="AT517" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU517" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV517" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW517" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX517" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY517" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA517" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB517" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC517" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -86890,7 +87035,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -86973,7 +87118,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10">
@@ -86983,7 +87128,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11">
@@ -87035,7 +87180,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>640634</v>
+        <v>640907</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -11398,13 +11398,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O67" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R67" t="n">
-        <v>0.2242771302788003</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -11562,10 +11562,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O68" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -11806,9 +11806,6 @@
       <c r="O69" t="n">
         <v>107</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.03065590802063242</v>
       </c>
@@ -12107,9 +12104,6 @@
       <c r="O71" t="n">
         <v>39</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -12403,16 +12397,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O73" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R73" t="n">
-        <v>0.009454625838138971</v>
+        <v>0.008595114398308155</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -12704,16 +12695,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O75" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R75" t="n">
-        <v>0.01174665634435448</v>
+        <v>0.01146015253107754</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13010,9 +12998,6 @@
       <c r="O77" t="n">
         <v>26</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.007449099145200401</v>
       </c>
@@ -23787,13 +23772,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O143" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R143" t="n">
-        <v>0.214932249850517</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -23951,10 +23936,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O144" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -24338,16 +24323,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O146" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R146" t="n">
-        <v>0.01289267159746223</v>
+        <v>0.01231966397090836</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24644,9 +24626,6 @@
       <c r="O148" t="n">
         <v>47</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.01346567922401611</v>
       </c>
@@ -24945,9 +24924,6 @@
       <c r="O150" t="n">
         <v>40</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01146015253107754</v>
       </c>
@@ -25241,16 +25217,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O152" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R152" t="n">
-        <v>0.01461169447712387</v>
+        <v>0.01432519066384693</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -36212,9 +36185,6 @@
       <c r="O219" t="n">
         <v>71</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.02034177074266263</v>
       </c>
@@ -36508,16 +36478,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O221" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R221" t="n">
-        <v>0.02406632031526284</v>
+        <v>0.0237798165019859</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -36814,9 +36781,6 @@
       <c r="O223" t="n">
         <v>37</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -37115,9 +37079,6 @@
       <c r="O225" t="n">
         <v>56</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.01604421354350856</v>
       </c>
@@ -47510,13 +47471,13 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O289" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R289" t="n">
-        <v>0.2336220107070837</v>
+        <v>0.2242771302788003</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -47674,10 +47635,10 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O290" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U290" t="inlineStr">
         <is>
@@ -48061,16 +48022,13 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O292" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q292" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R292" t="n">
-        <v>0.01547120591695468</v>
+        <v>0.01518470210367774</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -48362,16 +48320,13 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O294" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="R294" t="n">
-        <v>0.0200552669293857</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -48668,9 +48623,6 @@
       <c r="O296" t="n">
         <v>60</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.01719022879661631</v>
       </c>
@@ -48964,16 +48916,13 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O298" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q298" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R298" t="n">
-        <v>0.02435282412853977</v>
+        <v>0.02406632031526284</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
@@ -55942,13 +55891,13 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O337" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R337" t="n">
-        <v>0.2055873694222336</v>
+        <v>0.1962424889939503</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
@@ -56106,10 +56055,10 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O338" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U338" t="inlineStr">
         <is>
@@ -56493,16 +56442,13 @@
         </is>
       </c>
       <c r="N340" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O340" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R340" t="n">
-        <v>0.0148981982904008</v>
+        <v>0.01432519066384693</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
@@ -56794,16 +56740,13 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O342" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q342" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R342" t="n">
-        <v>0.01346567922401611</v>
+        <v>0.01317917541073917</v>
       </c>
       <c r="S342" t="inlineStr">
         <is>
@@ -57095,16 +57038,13 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O344" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q344" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="R344" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.02034177074266263</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
@@ -57401,9 +57341,6 @@
       <c r="O346" t="n">
         <v>59</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.01690372498333937</v>
       </c>
@@ -64287,13 +64224,13 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O385" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R385" t="n">
-        <v>0.2336220107070837</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
@@ -64451,10 +64388,10 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O386" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="U386" t="inlineStr">
         <is>
@@ -86999,6 +86936,156 @@
       <c r="BC517" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N518" t="n">
+        <v>61</v>
+      </c>
+      <c r="O518" t="n">
+        <v>61</v>
+      </c>
+      <c r="R518" t="n">
+        <v>0.01747673260989325</v>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO518" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP518" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR518" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS518" t="inlineStr"/>
+      <c r="AT518" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU518" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV518" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW518" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX518" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY518" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA518" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB518" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC518" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -87035,7 +87122,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -87118,7 +87205,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10">
@@ -87128,7 +87215,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11">
@@ -87180,7 +87267,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>640907</v>
+        <v>640943</v>
       </c>
     </row>
     <row r="16">
